--- a/CLB07N.xlsx
+++ b/CLB07N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2100" uniqueCount="758">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2124" uniqueCount="766">
   <si>
     <t/>
   </si>
@@ -532,13 +532,13 @@
     <t>20134557</t>
   </si>
   <si>
-    <t>OATSIDE CRML MCHT200</t>
+    <t>OATSIDE CRML MCHT240</t>
   </si>
   <si>
     <t>20129108</t>
   </si>
   <si>
-    <t>OATSDE COFFEE 200</t>
+    <t>OATSDE COFFEE 240ML</t>
   </si>
   <si>
     <t>20114494</t>
@@ -1366,6 +1366,18 @@
     <t>PORORO APEL 235ML</t>
   </si>
   <si>
+    <t>20141361</t>
+  </si>
+  <si>
+    <t>PORORO ZERO STRW 235</t>
+  </si>
+  <si>
+    <t>20141360</t>
+  </si>
+  <si>
+    <t>PORORO ZERO MILK 235</t>
+  </si>
+  <si>
     <t>20019179</t>
   </si>
   <si>
@@ -1517,6 +1529,18 @@
   </si>
   <si>
     <t>YOU C1000 LMN WTR500</t>
+  </si>
+  <si>
+    <t>20141600</t>
+  </si>
+  <si>
+    <t>IDM ISOTONC FRUIT350</t>
+  </si>
+  <si>
+    <t>20141601</t>
+  </si>
+  <si>
+    <t>IDM ISOTONC LYCHE350</t>
   </si>
   <si>
     <t>20015838</t>
@@ -2677,7 +2701,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F350"/>
+  <dimension ref="A1:F354"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -6861,7 +6885,7 @@
         <v>440</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>126</v>
+        <v>37</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>23</v>
@@ -6878,30 +6902,30 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B211" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="B211" s="1" t="s">
-        <v>457</v>
-      </c>
       <c r="C211" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>8</v>
+        <v>126</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>23</v>
@@ -6909,22 +6933,22 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B212" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="B212" s="1" t="s">
+      <c r="C212" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D212" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="C212" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D212" s="1" t="s">
-        <v>455</v>
-      </c>
       <c r="E212" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -6938,13 +6962,13 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -6958,13 +6982,13 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -6978,13 +7002,13 @@
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -6998,10 +7022,10 @@
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>23</v>
@@ -7018,10 +7042,10 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>23</v>
@@ -7038,13 +7062,13 @@
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>126</v>
+        <v>37</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -7058,10 +7082,10 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>145</v>
+        <v>40</v>
       </c>
       <c r="F219" s="1" t="s">
         <v>23</v>
@@ -7078,30 +7102,30 @@
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>476</v>
+        <v>459</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>4</v>
+        <v>126</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B221" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="B221" s="1" t="s">
-        <v>478</v>
-      </c>
       <c r="C221" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>476</v>
+        <v>459</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>8</v>
+        <v>145</v>
       </c>
       <c r="F221" s="1" t="s">
         <v>23</v>
@@ -7109,19 +7133,19 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B222" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="B222" s="1" t="s">
+      <c r="C222" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D222" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="C222" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D222" s="1" t="s">
-        <v>476</v>
-      </c>
       <c r="E222" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F222" s="1" t="s">
         <v>23</v>
@@ -7138,10 +7162,10 @@
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F223" s="1" t="s">
         <v>23</v>
@@ -7158,10 +7182,10 @@
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F224" s="1" t="s">
         <v>23</v>
@@ -7178,10 +7202,10 @@
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F225" s="1" t="s">
         <v>23</v>
@@ -7198,13 +7222,13 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -7218,13 +7242,13 @@
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -7238,10 +7262,10 @@
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="F228" s="1" t="s">
         <v>28</v>
@@ -7249,19 +7273,19 @@
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="B229" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="B229" s="1" t="s">
-        <v>495</v>
-      </c>
       <c r="C229" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="F229" s="1" t="s">
         <v>28</v>
@@ -7269,19 +7293,19 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="B230" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="B230" s="1" t="s">
+      <c r="C230" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D230" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="C230" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D230" s="1" t="s">
-        <v>493</v>
-      </c>
       <c r="E230" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F230" s="1" t="s">
         <v>28</v>
@@ -7298,13 +7322,13 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -7318,13 +7342,13 @@
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -7338,90 +7362,90 @@
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="B234" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="B234" s="1" t="s">
-        <v>506</v>
-      </c>
       <c r="C234" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="B235" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="B235" s="1" t="s">
-        <v>508</v>
-      </c>
       <c r="C235" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>28</v>
+        <v>163</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="B236" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="B236" s="1" t="s">
-        <v>510</v>
-      </c>
       <c r="C236" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>28</v>
+        <v>163</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="B237" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="B237" s="1" t="s">
+      <c r="C237" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D237" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="C237" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D237" s="1" t="s">
-        <v>504</v>
-      </c>
       <c r="E237" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F237" s="1" t="s">
         <v>28</v>
@@ -7438,13 +7462,13 @@
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>163</v>
+        <v>28</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
@@ -7458,13 +7482,13 @@
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>163</v>
+        <v>28</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -7478,133 +7502,133 @@
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>519</v>
+        <v>28</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="B241" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="B241" s="1" t="s">
-        <v>521</v>
-      </c>
       <c r="C241" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="B242" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="B242" s="1" t="s">
-        <v>523</v>
-      </c>
       <c r="C242" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>23</v>
+        <v>163</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>23</v>
+        <v>163</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="B244" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="C244" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D244" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="E244" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F244" s="1" t="s">
         <v>527</v>
-      </c>
-      <c r="B244" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="C244" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D244" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="E244" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F244" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="B245" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="B245" s="1" t="s">
-        <v>530</v>
-      </c>
       <c r="C245" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>14</v>
+        <v>126</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="B246" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="B246" s="1" t="s">
+      <c r="C246" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D246" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="C246" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D246" s="1" t="s">
-        <v>524</v>
-      </c>
       <c r="E246" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -7618,13 +7642,13 @@
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -7638,13 +7662,13 @@
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -7658,13 +7682,13 @@
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -7678,93 +7702,93 @@
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B251" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="B251" s="1" t="s">
-        <v>543</v>
-      </c>
       <c r="C251" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B252" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="B252" s="1" t="s">
-        <v>545</v>
-      </c>
       <c r="C252" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="B253" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="B253" s="1" t="s">
-        <v>547</v>
-      </c>
       <c r="C253" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="B254" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="B254" s="1" t="s">
+      <c r="C254" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D254" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="C254" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D254" s="1" t="s">
-        <v>541</v>
-      </c>
       <c r="E254" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -7778,10 +7802,10 @@
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F255" s="1" t="s">
         <v>23</v>
@@ -7798,10 +7822,10 @@
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="F256" s="1" t="s">
         <v>23</v>
@@ -7818,10 +7842,10 @@
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="F257" s="1" t="s">
         <v>23</v>
@@ -7838,33 +7862,33 @@
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="B259" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="B259" s="1" t="s">
-        <v>557</v>
-      </c>
       <c r="C259" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -7878,10 +7902,10 @@
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="F260" s="1" t="s">
         <v>23</v>
@@ -7898,10 +7922,10 @@
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="F261" s="1" t="s">
         <v>23</v>
@@ -7918,33 +7942,33 @@
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B263" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="C263" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D263" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="B263" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="C263" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D263" s="1" t="s">
-        <v>558</v>
-      </c>
       <c r="E263" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -7958,10 +7982,10 @@
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="F264" s="1" t="s">
         <v>23</v>
@@ -7978,10 +8002,10 @@
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="F265" s="1" t="s">
         <v>23</v>
@@ -7998,10 +8022,10 @@
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="F266" s="1" t="s">
         <v>23</v>
@@ -8018,10 +8042,10 @@
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F267" s="1" t="s">
         <v>23</v>
@@ -8029,19 +8053,19 @@
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="B268" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="B268" s="1" t="s">
-        <v>578</v>
-      </c>
       <c r="C268" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="F268" s="1" t="s">
         <v>23</v>
@@ -8049,19 +8073,19 @@
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="B269" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="B269" s="1" t="s">
-        <v>580</v>
-      </c>
       <c r="C269" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="F269" s="1" t="s">
         <v>23</v>
@@ -8069,19 +8093,19 @@
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="B270" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="B270" s="1" t="s">
-        <v>582</v>
-      </c>
       <c r="C270" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>14</v>
+        <v>126</v>
       </c>
       <c r="F270" s="1" t="s">
         <v>23</v>
@@ -8089,19 +8113,19 @@
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="B271" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="B271" s="1" t="s">
+      <c r="C271" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D271" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="C271" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D271" s="1" t="s">
-        <v>576</v>
-      </c>
       <c r="E271" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F271" s="1" t="s">
         <v>23</v>
@@ -8118,10 +8142,10 @@
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F272" s="1" t="s">
         <v>23</v>
@@ -8138,10 +8162,10 @@
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>23</v>
@@ -8158,10 +8182,10 @@
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>23</v>
@@ -8178,10 +8202,10 @@
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="F275" s="1" t="s">
         <v>23</v>
@@ -8198,10 +8222,10 @@
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>145</v>
+        <v>20</v>
       </c>
       <c r="F276" s="1" t="s">
         <v>23</v>
@@ -8218,10 +8242,10 @@
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>162</v>
+        <v>37</v>
       </c>
       <c r="F277" s="1" t="s">
         <v>23</v>
@@ -8238,10 +8262,10 @@
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>599</v>
+        <v>584</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F278" s="1" t="s">
         <v>23</v>
@@ -8249,19 +8273,19 @@
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="B279" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="B279" s="1" t="s">
-        <v>601</v>
-      </c>
       <c r="C279" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>599</v>
+        <v>584</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>8</v>
+        <v>126</v>
       </c>
       <c r="F279" s="1" t="s">
         <v>23</v>
@@ -8269,19 +8293,19 @@
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B280" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="B280" s="1" t="s">
-        <v>603</v>
-      </c>
       <c r="C280" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>599</v>
+        <v>584</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>11</v>
+        <v>145</v>
       </c>
       <c r="F280" s="1" t="s">
         <v>23</v>
@@ -8289,19 +8313,19 @@
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="B281" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="B281" s="1" t="s">
-        <v>605</v>
-      </c>
       <c r="C281" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>599</v>
+        <v>584</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>14</v>
+        <v>162</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>23</v>
@@ -8309,19 +8333,19 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="B282" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="B282" s="1" t="s">
+      <c r="C282" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D282" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="C282" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D282" s="1" t="s">
-        <v>599</v>
-      </c>
       <c r="E282" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F282" s="1" t="s">
         <v>23</v>
@@ -8338,10 +8362,10 @@
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F283" s="1" t="s">
         <v>23</v>
@@ -8358,30 +8382,30 @@
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>612</v>
+        <v>23</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="B285" s="1" t="s">
         <v>613</v>
       </c>
-      <c r="B285" s="1" t="s">
-        <v>614</v>
-      </c>
       <c r="C285" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="F285" s="1" t="s">
         <v>23</v>
@@ -8389,19 +8413,19 @@
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="B286" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="B286" s="1" t="s">
-        <v>616</v>
-      </c>
       <c r="C286" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="F286" s="1" t="s">
         <v>23</v>
@@ -8409,19 +8433,19 @@
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="B287" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="B287" s="1" t="s">
-        <v>618</v>
-      </c>
       <c r="C287" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>145</v>
+        <v>20</v>
       </c>
       <c r="F287" s="1" t="s">
         <v>23</v>
@@ -8429,102 +8453,102 @@
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="B288" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="B288" s="1" t="s">
+      <c r="C288" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D288" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="E288" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F288" s="1" t="s">
         <v>620</v>
-      </c>
-      <c r="C288" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D288" s="1" t="s">
-        <v>621</v>
-      </c>
-      <c r="E288" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F288" s="1" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="B289" s="1" t="s">
         <v>622</v>
       </c>
-      <c r="B289" s="1" t="s">
-        <v>623</v>
-      </c>
       <c r="C289" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>621</v>
+        <v>607</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>612</v>
+        <v>23</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="B290" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="B290" s="1" t="s">
-        <v>625</v>
-      </c>
       <c r="C290" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>621</v>
+        <v>607</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>11</v>
+        <v>126</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>612</v>
+        <v>23</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="B291" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="B291" s="1" t="s">
-        <v>627</v>
-      </c>
       <c r="C291" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>621</v>
+        <v>607</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>14</v>
+        <v>145</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>612</v>
+        <v>23</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="B292" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="B292" s="1" t="s">
+      <c r="C292" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D292" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="C292" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D292" s="1" t="s">
-        <v>621</v>
-      </c>
       <c r="E292" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -8538,13 +8562,13 @@
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -8558,13 +8582,13 @@
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -8578,13 +8602,13 @@
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -8598,13 +8622,13 @@
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -8618,90 +8642,90 @@
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>640</v>
+        <v>629</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>23</v>
+        <v>620</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="B298" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="B298" s="1" t="s">
-        <v>642</v>
-      </c>
       <c r="C298" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>640</v>
+        <v>629</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>23</v>
+        <v>620</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="B299" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="B299" s="1" t="s">
-        <v>644</v>
-      </c>
       <c r="C299" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>640</v>
+        <v>629</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>23</v>
+        <v>620</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="B300" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="B300" s="1" t="s">
-        <v>646</v>
-      </c>
       <c r="C300" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>640</v>
+        <v>629</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>14</v>
+        <v>126</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>23</v>
+        <v>620</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="B301" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="B301" s="1" t="s">
+      <c r="C301" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D301" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="C301" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D301" s="1" t="s">
-        <v>640</v>
-      </c>
       <c r="E301" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>23</v>
@@ -8718,10 +8742,10 @@
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>23</v>
@@ -8738,10 +8762,10 @@
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="F303" s="1" t="s">
         <v>23</v>
@@ -8758,10 +8782,10 @@
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="F304" s="1" t="s">
         <v>23</v>
@@ -8778,10 +8802,10 @@
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="F305" s="1" t="s">
         <v>23</v>
@@ -8798,10 +8822,10 @@
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>659</v>
+        <v>648</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F306" s="1" t="s">
         <v>23</v>
@@ -8809,19 +8833,19 @@
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="B307" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="B307" s="1" t="s">
-        <v>661</v>
-      </c>
       <c r="C307" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>659</v>
+        <v>648</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="F307" s="1" t="s">
         <v>23</v>
@@ -8829,19 +8853,19 @@
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="B308" s="1" t="s">
         <v>662</v>
       </c>
-      <c r="B308" s="1" t="s">
-        <v>663</v>
-      </c>
       <c r="C308" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>659</v>
+        <v>648</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="F308" s="1" t="s">
         <v>23</v>
@@ -8849,19 +8873,19 @@
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="B309" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="B309" s="1" t="s">
-        <v>665</v>
-      </c>
       <c r="C309" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>659</v>
+        <v>648</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>14</v>
+        <v>126</v>
       </c>
       <c r="F309" s="1" t="s">
         <v>23</v>
@@ -8869,19 +8893,19 @@
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="B310" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="B310" s="1" t="s">
+      <c r="C310" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D310" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="C310" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D310" s="1" t="s">
-        <v>659</v>
-      </c>
       <c r="E310" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F310" s="1" t="s">
         <v>23</v>
@@ -8898,10 +8922,10 @@
         <v>3</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>23</v>
@@ -8918,10 +8942,10 @@
         <v>3</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="F312" s="1" t="s">
         <v>23</v>
@@ -8938,10 +8962,10 @@
         <v>3</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="F313" s="1" t="s">
         <v>23</v>
@@ -8958,10 +8982,10 @@
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="F314" s="1" t="s">
         <v>23</v>
@@ -8978,10 +9002,10 @@
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>678</v>
+        <v>667</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F315" s="1" t="s">
         <v>23</v>
@@ -8989,19 +9013,19 @@
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="B316" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="B316" s="1" t="s">
-        <v>680</v>
-      </c>
       <c r="C316" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>678</v>
+        <v>667</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="F316" s="1" t="s">
         <v>23</v>
@@ -9009,19 +9033,19 @@
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="B317" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="B317" s="1" t="s">
-        <v>682</v>
-      </c>
       <c r="C317" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>678</v>
+        <v>667</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="F317" s="1" t="s">
         <v>23</v>
@@ -9029,19 +9053,19 @@
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="B318" s="1" t="s">
         <v>683</v>
       </c>
-      <c r="B318" s="1" t="s">
-        <v>684</v>
-      </c>
       <c r="C318" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>678</v>
+        <v>667</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>14</v>
+        <v>126</v>
       </c>
       <c r="F318" s="1" t="s">
         <v>23</v>
@@ -9049,19 +9073,19 @@
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="B319" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="B319" s="1" t="s">
+      <c r="C319" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D319" s="1" t="s">
         <v>686</v>
       </c>
-      <c r="C319" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D319" s="1" t="s">
-        <v>678</v>
-      </c>
       <c r="E319" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F319" s="1" t="s">
         <v>23</v>
@@ -9078,10 +9102,10 @@
         <v>3</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F320" s="1" t="s">
         <v>23</v>
@@ -9098,10 +9122,10 @@
         <v>3</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="F321" s="1" t="s">
         <v>23</v>
@@ -9118,10 +9142,10 @@
         <v>3</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="F322" s="1" t="s">
         <v>23</v>
@@ -9138,10 +9162,10 @@
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="F323" s="1" t="s">
         <v>23</v>
@@ -9158,10 +9182,10 @@
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>697</v>
+        <v>686</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F324" s="1" t="s">
         <v>23</v>
@@ -9169,19 +9193,19 @@
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="B325" s="1" t="s">
         <v>698</v>
       </c>
-      <c r="B325" s="1" t="s">
-        <v>699</v>
-      </c>
       <c r="C325" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>697</v>
+        <v>686</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="F325" s="1" t="s">
         <v>23</v>
@@ -9189,59 +9213,59 @@
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="B326" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="B326" s="1" t="s">
-        <v>701</v>
-      </c>
       <c r="C326" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>697</v>
+        <v>686</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="B327" s="1" t="s">
         <v>702</v>
       </c>
-      <c r="B327" s="1" t="s">
-        <v>703</v>
-      </c>
       <c r="C327" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>697</v>
+        <v>686</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>14</v>
+        <v>126</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B328" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="B328" s="1" t="s">
+      <c r="C328" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D328" s="1" t="s">
         <v>705</v>
       </c>
-      <c r="C328" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D328" s="1" t="s">
-        <v>697</v>
-      </c>
       <c r="E328" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F328" s="1" t="s">
         <v>23</v>
@@ -9258,10 +9282,10 @@
         <v>3</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F329" s="1" t="s">
         <v>23</v>
@@ -9278,13 +9302,13 @@
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -9298,13 +9322,13 @@
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -9318,10 +9342,10 @@
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="F332" s="1" t="s">
         <v>23</v>
@@ -9338,10 +9362,10 @@
         <v>3</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>145</v>
+        <v>20</v>
       </c>
       <c r="F333" s="1" t="s">
         <v>23</v>
@@ -9358,50 +9382,50 @@
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>718</v>
+        <v>705</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="B335" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="B335" s="1" t="s">
-        <v>720</v>
-      </c>
       <c r="C335" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>718</v>
+        <v>705</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="B336" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="B336" s="1" t="s">
-        <v>722</v>
-      </c>
       <c r="C336" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>718</v>
+        <v>705</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>11</v>
+        <v>126</v>
       </c>
       <c r="F336" s="1" t="s">
         <v>23</v>
@@ -9409,42 +9433,42 @@
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="B337" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="B337" s="1" t="s">
-        <v>724</v>
-      </c>
       <c r="C337" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>718</v>
+        <v>705</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>14</v>
+        <v>145</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="B338" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="B338" s="1" t="s">
+      <c r="C338" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D338" s="1" t="s">
         <v>726</v>
       </c>
-      <c r="C338" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D338" s="1" t="s">
-        <v>718</v>
-      </c>
       <c r="E338" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
@@ -9458,13 +9482,13 @@
         <v>3</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
@@ -9478,13 +9502,13 @@
         <v>3</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
@@ -9498,50 +9522,50 @@
         <v>3</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>733</v>
+        <v>28</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="B342" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="B342" s="1" t="s">
-        <v>735</v>
-      </c>
       <c r="C342" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="B343" s="1" t="s">
         <v>736</v>
       </c>
-      <c r="B343" s="1" t="s">
-        <v>737</v>
-      </c>
       <c r="C343" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>738</v>
+        <v>726</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F343" s="1" t="s">
         <v>23</v>
@@ -9549,59 +9573,59 @@
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>738</v>
+        <v>726</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="B345" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="C345" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D345" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="E345" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F345" s="1" t="s">
         <v>741</v>
-      </c>
-      <c r="B345" s="1" t="s">
-        <v>742</v>
-      </c>
-      <c r="C345" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D345" s="1" t="s">
-        <v>743</v>
-      </c>
-      <c r="E345" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F345" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>746</v>
+        <v>726</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>4</v>
+        <v>126</v>
       </c>
       <c r="F346" s="1" t="s">
         <v>70</v>
@@ -9609,81 +9633,161 @@
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="E347" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>750</v>
+        <v>23</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="E348" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>753</v>
+        <v>23</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>753</v>
+        <v>23</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="B350" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="C350" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D350" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="E350" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F350" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A351" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="B351" s="1" t="s">
         <v>756</v>
       </c>
-      <c r="B350" s="1" t="s">
+      <c r="C351" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D351" s="1" t="s">
         <v>757</v>
       </c>
-      <c r="C350" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D350" s="1" t="s">
-        <v>749</v>
-      </c>
-      <c r="E350" s="1" t="s">
+      <c r="E351" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F351" s="1" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A352" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="B352" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="C352" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D352" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="E352" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F352" s="1" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A353" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="B353" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="C353" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D353" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="E353" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F353" s="1" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A354" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="B354" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="C354" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D354" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="E354" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F350" s="1" t="s">
+      <c r="F354" s="1" t="s">
         <v>23</v>
       </c>
     </row>
